--- a/output/paket/06_YATIRIM DOSYASI/GYM MALTEPE — ANA BoQ (111 poz).xlsx
+++ b/output/paket/06_YATIRIM DOSYASI/GYM MALTEPE — ANA BoQ (111 poz).xlsx
@@ -808,7 +808,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev G · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev H · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Net iç alan 103.78 m²</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Net iç alan 103.78 m²</t>
         </is>
       </c>
     </row>

--- a/output/paket/06_YATIRIM DOSYASI/GYM MALTEPE — ANA BoQ (111 poz).xlsx
+++ b/output/paket/06_YATIRIM DOSYASI/GYM MALTEPE — ANA BoQ (111 poz).xlsx
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="E8" s="37" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="F8" s="30" t="n"/>
       <c r="G8" s="38">
@@ -1757,11 +1757,11 @@
         <v/>
       </c>
       <c r="H8" s="39">
-        <f>138260*K8</f>
+        <f>139810*K8</f>
         <v/>
       </c>
       <c r="I8" s="39">
-        <f>173940*K8</f>
+        <f>175890*K8</f>
         <v/>
       </c>
       <c r="J8" s="40" t="inlineStr">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="E9" s="44" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="F9" s="30" t="n"/>
       <c r="G9" s="45">
@@ -1803,11 +1803,11 @@
         <v/>
       </c>
       <c r="H9" s="46">
-        <f>7035*K9</f>
+        <f>7105*K9</f>
         <v/>
       </c>
       <c r="I9" s="46">
-        <f>10452*K9</f>
+        <f>10556*K9</f>
         <v/>
       </c>
       <c r="J9" s="47" t="inlineStr">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="E10" s="37" t="n">
-        <v>129.3</v>
+        <v>131.8</v>
       </c>
       <c r="F10" s="30" t="n"/>
       <c r="G10" s="38">
@@ -1849,11 +1849,11 @@
         <v/>
       </c>
       <c r="H10" s="39">
-        <f>49134*K10</f>
+        <f>50084*K10</f>
         <v/>
       </c>
       <c r="I10" s="39">
-        <f>72408*K10</f>
+        <f>73808*K10</f>
         <v/>
       </c>
       <c r="J10" s="40" t="inlineStr">
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="F12" s="30" t="n"/>
       <c r="G12" s="38">
@@ -1942,11 +1942,11 @@
         <v/>
       </c>
       <c r="H12" s="39">
-        <f>19440*K12</f>
+        <f>19520*K12</f>
         <v/>
       </c>
       <c r="I12" s="39">
-        <f>26730*K12</f>
+        <f>26840*K12</f>
         <v/>
       </c>
       <c r="J12" s="40" t="inlineStr">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>55.7</v>
+        <v>56.4</v>
       </c>
       <c r="F14" s="30" t="n"/>
       <c r="G14" s="38">
@@ -2034,11 +2034,11 @@
         <v/>
       </c>
       <c r="H14" s="39">
-        <f>99982*K14</f>
+        <f>101238*K14</f>
         <v/>
       </c>
       <c r="I14" s="39">
-        <f>147605*K14</f>
+        <f>149460*K14</f>
         <v/>
       </c>
       <c r="J14" s="40" t="inlineStr">
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="E19" s="44" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="F19" s="30" t="n"/>
       <c r="G19" s="45">
@@ -2266,11 +2266,11 @@
         <v/>
       </c>
       <c r="H19" s="46">
-        <f>87340*K19</f>
+        <f>87835*K19</f>
         <v/>
       </c>
       <c r="I19" s="46">
-        <f>124499*K19</f>
+        <f>125205*K19</f>
         <v/>
       </c>
       <c r="J19" s="47" t="inlineStr">
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="E20" s="37" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="F20" s="30" t="n"/>
       <c r="G20" s="38">
@@ -2312,11 +2312,11 @@
         <v/>
       </c>
       <c r="H20" s="39">
-        <f>26361*K20</f>
+        <f>26510*K20</f>
         <v/>
       </c>
       <c r="I20" s="39">
-        <f>40018*K20</f>
+        <f>40244*K20</f>
         <v/>
       </c>
       <c r="J20" s="40" t="inlineStr">
@@ -2351,7 +2351,7 @@
         </is>
       </c>
       <c r="E21" s="44" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="F21" s="30" t="n"/>
       <c r="G21" s="45">
@@ -2359,11 +2359,11 @@
         <v/>
       </c>
       <c r="H21" s="46">
-        <f>36812*K21</f>
+        <f>36861*K21</f>
         <v/>
       </c>
       <c r="I21" s="46">
-        <f>53544*K21</f>
+        <f>53616*K21</f>
         <v/>
       </c>
       <c r="J21" s="47" t="inlineStr">
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="E22" s="37" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="38">
@@ -2405,11 +2405,11 @@
         <v/>
       </c>
       <c r="H22" s="39">
-        <f>45183*K22</f>
+        <f>44895*K22</f>
         <v/>
       </c>
       <c r="I22" s="39">
-        <f>69918*K22</f>
+        <f>69472*K22</f>
         <v/>
       </c>
       <c r="J22" s="40" t="inlineStr">
@@ -2443,7 +2443,7 @@
         </is>
       </c>
       <c r="E23" s="44" t="n">
-        <v>71.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F23" s="30" t="n"/>
       <c r="G23" s="45">
@@ -2451,11 +2451,11 @@
         <v/>
       </c>
       <c r="H23" s="46">
-        <f>25025*K23</f>
+        <f>25410*K23</f>
         <v/>
       </c>
       <c r="I23" s="46">
-        <f>39325*K23</f>
+        <f>39930*K23</f>
         <v/>
       </c>
       <c r="J23" s="47" t="inlineStr">
@@ -2489,7 +2489,7 @@
         </is>
       </c>
       <c r="E24" s="37" t="n">
-        <v>129.3</v>
+        <v>131.8</v>
       </c>
       <c r="F24" s="30" t="n"/>
       <c r="G24" s="38">
@@ -2497,11 +2497,11 @@
         <v/>
       </c>
       <c r="H24" s="39">
-        <f>49781*K24</f>
+        <f>50743*K24</f>
         <v/>
       </c>
       <c r="I24" s="39">
-        <f>78873*K24</f>
+        <f>80398*K24</f>
         <v/>
       </c>
       <c r="J24" s="40" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="E46" s="37" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="F46" s="30" t="n"/>
       <c r="G46" s="38">
@@ -3513,11 +3513,11 @@
         <v/>
       </c>
       <c r="H46" s="39">
-        <f>12075*K46</f>
+        <f>12190*K46</f>
         <v/>
       </c>
       <c r="I46" s="39">
-        <f>19950*K46</f>
+        <f>20140*K46</f>
         <v/>
       </c>
       <c r="J46" s="40" t="inlineStr">
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="E47" s="44" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="F47" s="30" t="n"/>
       <c r="G47" s="45">
@@ -3559,11 +3559,11 @@
         <v/>
       </c>
       <c r="H47" s="46">
-        <f>2728*K47</f>
+        <f>3162*K47</f>
         <v/>
       </c>
       <c r="I47" s="46">
-        <f>4620*K47</f>
+        <f>5355*K47</f>
         <v/>
       </c>
       <c r="J47" s="47" t="inlineStr">
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F48" s="30" t="n"/>
       <c r="G48" s="38">
@@ -3605,11 +3605,11 @@
         <v/>
       </c>
       <c r="H48" s="39">
-        <f>1260*K48</f>
+        <f>1050*K48</f>
         <v/>
       </c>
       <c r="I48" s="39">
-        <f>2160*K48</f>
+        <f>1800*K48</f>
         <v/>
       </c>
       <c r="J48" s="40" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E49" s="44" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="F49" s="30" t="n"/>
       <c r="G49" s="45">
@@ -3651,11 +3651,11 @@
         <v/>
       </c>
       <c r="H49" s="46">
-        <f>8100*K49</f>
+        <f>9018*K49</f>
         <v/>
       </c>
       <c r="I49" s="46">
-        <f>13500*K49</f>
+        <f>15030*K49</f>
         <v/>
       </c>
       <c r="J49" s="47" t="inlineStr">
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="E56" s="37" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="F56" s="30" t="n"/>
       <c r="G56" s="38">
@@ -3973,11 +3973,11 @@
         <v/>
       </c>
       <c r="H56" s="39">
-        <f>27690*K56</f>
+        <f>27768*K56</f>
         <v/>
       </c>
       <c r="I56" s="39">
-        <f>46150*K56</f>
+        <f>46280*K56</f>
         <v/>
       </c>
       <c r="J56" s="40" t="inlineStr">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="E57" s="44" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="F57" s="30" t="n"/>
       <c r="G57" s="45">
@@ -4019,11 +4019,11 @@
         <v/>
       </c>
       <c r="H57" s="46">
-        <f>13536*K57</f>
+        <f>14112*K57</f>
         <v/>
       </c>
       <c r="I57" s="46">
-        <f>22842*K57</f>
+        <f>23814*K57</f>
         <v/>
       </c>
       <c r="J57" s="47" t="inlineStr">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="E63" s="44" t="n">
-        <v>35.8</v>
+        <v>34</v>
       </c>
       <c r="F63" s="30" t="n"/>
       <c r="G63" s="45">
@@ -4297,11 +4297,11 @@
         <v/>
       </c>
       <c r="H63" s="46">
-        <f>39380*K63</f>
+        <f>37400*K63</f>
         <v/>
       </c>
       <c r="I63" s="46">
-        <f>66230*K63</f>
+        <f>62900*K63</f>
         <v/>
       </c>
       <c r="J63" s="47" t="inlineStr">
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="E65" s="44" t="n">
-        <v>34.2</v>
+        <v>31.9</v>
       </c>
       <c r="F65" s="30" t="n"/>
       <c r="G65" s="45">
@@ -4389,11 +4389,11 @@
         <v/>
       </c>
       <c r="H65" s="46">
-        <f>14364*K65</f>
+        <f>13398*K65</f>
         <v/>
       </c>
       <c r="I65" s="46">
-        <f>24624*K65</f>
+        <f>22968*K65</f>
         <v/>
       </c>
       <c r="J65" s="47" t="inlineStr">
@@ -6451,7 +6451,7 @@
         </is>
       </c>
       <c r="E110" s="37" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F110" s="30" t="n"/>
       <c r="G110" s="38">
@@ -6459,11 +6459,11 @@
         <v/>
       </c>
       <c r="H110" s="39">
-        <f>12600*K110</f>
+        <f>12720*K110</f>
         <v/>
       </c>
       <c r="I110" s="39">
-        <f>22050*K110</f>
+        <f>22260*K110</f>
         <v/>
       </c>
       <c r="J110" s="40" t="inlineStr">
@@ -7163,7 +7163,7 @@
         </is>
       </c>
       <c r="B10" s="61" t="n">
-        <v>46.15</v>
+        <v>46.91</v>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="B11" s="67" t="n">
-        <v>25.32</v>
+        <v>25.65</v>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="B12" s="61" t="n">
-        <v>129.3</v>
+        <v>131.8</v>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="B13" s="67" t="n">
-        <v>55.7</v>
+        <v>56.4</v>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         </is>
       </c>
       <c r="B14" s="61" t="n">
-        <v>44.6</v>
+        <v>45.1</v>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>

--- a/output/paket/06_YATIRIM DOSYASI/GYM MALTEPE — ANA BoQ (111 poz).xlsx
+++ b/output/paket/06_YATIRIM DOSYASI/GYM MALTEPE — ANA BoQ (111 poz).xlsx
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="E48" s="37" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="F48" s="30" t="n"/>
       <c r="G48" s="38">
@@ -3605,11 +3605,11 @@
         <v/>
       </c>
       <c r="H48" s="39">
-        <f>1050*K48</f>
+        <f>1260*K48</f>
         <v/>
       </c>
       <c r="I48" s="39">
-        <f>1800*K48</f>
+        <f>2160*K48</f>
         <v/>
       </c>
       <c r="J48" s="40" t="inlineStr">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E49" s="44" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="F49" s="30" t="n"/>
       <c r="G49" s="45">
@@ -3651,11 +3651,11 @@
         <v/>
       </c>
       <c r="H49" s="46">
-        <f>9018*K49</f>
+        <f>7506*K49</f>
         <v/>
       </c>
       <c r="I49" s="46">
-        <f>15030*K49</f>
+        <f>12510*K49</f>
         <v/>
       </c>
       <c r="J49" s="47" t="inlineStr">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="E57" s="44" t="n">
-        <v>44.1</v>
+        <v>41.3</v>
       </c>
       <c r="F57" s="30" t="n"/>
       <c r="G57" s="45">
@@ -4019,11 +4019,11 @@
         <v/>
       </c>
       <c r="H57" s="46">
-        <f>14112*K57</f>
+        <f>13216*K57</f>
         <v/>
       </c>
       <c r="I57" s="46">
-        <f>23814*K57</f>
+        <f>22302*K57</f>
         <v/>
       </c>
       <c r="J57" s="47" t="inlineStr">
